--- a/docs/MOJO_FPGA_pinout.xlsx
+++ b/docs/MOJO_FPGA_pinout.xlsx
@@ -4375,40 +4375,40 @@
         <v>238</v>
       </c>
       <c r="B2" s="10">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="1">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="13">
+        <v>1</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="str">
+      <c r="G2" s="13">
+        <v>15</v>
+      </c>
+      <c r="H2" s="13" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F2,"&lt;",G2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$F2,"&lt;",I2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1" t="str">
+        <v>NET "A&lt;15&gt;" LOC = P33 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="J2" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,I2,""" LOC = ",$C2," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "VPP" LOC = P33 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="K2" s="13">
+        <v>14</v>
+      </c>
+      <c r="L2" s="13" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F2,"&lt;",K2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;14&gt;" LOC = P33 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -4416,40 +4416,40 @@
         <v>238</v>
       </c>
       <c r="B3" s="10">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E3" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F3,"&lt;",G3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J3" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F3,"&lt;",I3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3" s="1" t="str">
-        <f t="shared" ref="L3:L15" si="0" xml:space="preserve"> CONCATENATE("NET """,$F3,"&lt;",K3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F3,"&lt;",K3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4457,40 +4457,40 @@
         <v>238</v>
       </c>
       <c r="B4" s="10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G4" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H4" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F4,"&lt;",G4,"&gt;"" LOC = ",$C4," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I4" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F4,"&lt;",I4,"&gt;"" LOC = ",$C4," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K4" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F4,"&lt;",K4,"&gt;"" LOC = ",$C4," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -4498,40 +4498,40 @@
         <v>238</v>
       </c>
       <c r="B5" s="10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E5" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G5" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F5,"&lt;",G5,"&gt;"" LOC = ",$C5," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I5" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F5,"&lt;",I5,"&gt;"" LOC = ",$C5," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K5" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F5,"&lt;",K5,"&gt;"" LOC = ",$C5," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -4539,40 +4539,40 @@
         <v>238</v>
       </c>
       <c r="B6" s="10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E6" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F6,"&lt;",G6,"&gt;"" LOC = ",$C6," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F6,"&lt;",I6,"&gt;"" LOC = ",$C6," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F6,"&lt;",K6,"&gt;"" LOC = ",$C6," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -4580,40 +4580,40 @@
         <v>238</v>
       </c>
       <c r="B7" s="10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G7" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F7,"&lt;",G7,"&gt;"" LOC = ",$C7," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F7,"&lt;",I7,"&gt;"" LOC = ",$C7," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K7" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F7,"&lt;",K7,"&gt;"" LOC = ",$C7," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -4621,40 +4621,40 @@
         <v>238</v>
       </c>
       <c r="B8" s="10">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E8" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G8" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F8,"&lt;",G8,"&gt;"" LOC = ",$C8," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I8" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J8" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F8,"&lt;",I8,"&gt;"" LOC = ",$C8," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K8" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F8,"&lt;",K8,"&gt;"" LOC = ",$C8," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -4662,40 +4662,40 @@
         <v>238</v>
       </c>
       <c r="B9" s="10">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E9" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G9" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F9,"&lt;",G9,"&gt;"" LOC = ",$C9," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I9" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J9" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F9,"&lt;",I9,"&gt;"" LOC = ",$C9," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K9" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F9,"&lt;",K9,"&gt;"" LOC = ",$C9," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -4703,40 +4703,40 @@
         <v>238</v>
       </c>
       <c r="B10" s="10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E10" s="1">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G10" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F10,"&lt;",G10,"&gt;"" LOC = ",$C10," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I10" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J10" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F10,"&lt;",I10,"&gt;"" LOC = ",$C10," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K10" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F10,"&lt;",K10,"&gt;"" LOC = ",$C10," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -4744,40 +4744,40 @@
         <v>238</v>
       </c>
       <c r="B11" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E11" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G11" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F11,"&lt;",G11,"&gt;"" LOC = ",$C11," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I11" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F11,"&lt;",I11,"&gt;"" LOC = ",$C11," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K11" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F11,"&lt;",K11,"&gt;"" LOC = ",$C11," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -4785,40 +4785,40 @@
         <v>238</v>
       </c>
       <c r="B12" s="10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E12" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="G12" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F12,"&lt;",G12,"&gt;"" LOC = ",$C12," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I12" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F12,"&lt;",I12,"&gt;"" LOC = ",$C12," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K12" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F12,"&lt;",K12,"&gt;"" LOC = ",$C12," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -4826,40 +4826,40 @@
         <v>238</v>
       </c>
       <c r="B13" s="10">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E13" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="G13" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F13,"&lt;",G13,"&gt;"" LOC = ",$C13," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I13" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F13,"&lt;",I13,"&gt;"" LOC = ",$C13," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K13" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F13,"&lt;",K13,"&gt;"" LOC = ",$C13," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -4867,40 +4867,40 @@
         <v>238</v>
       </c>
       <c r="B14" s="10">
+        <v>35</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G14" s="1">
         <v>2</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G14" s="1">
-        <v>12</v>
       </c>
       <c r="H14" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F14,"&lt;",G14,"&gt;"" LOC = ",$C14," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I14" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J14" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F14,"&lt;",I14,"&gt;"" LOC = ",$C14," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K14" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F14,"&lt;",K14,"&gt;"" LOC = ",$C14," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -4908,40 +4908,40 @@
         <v>238</v>
       </c>
       <c r="B15" s="10">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>164</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="G15" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H15" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F15,"&lt;",G15,"&gt;"" LOC = ",$C15," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I15" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J15" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F15,"&lt;",I15,"&gt;"" LOC = ",$C15," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K15" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F15,"&lt;",K15,"&gt;"" LOC = ",$C15," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -4949,40 +4949,40 @@
         <v>238</v>
       </c>
       <c r="B16" s="10">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>159</v>
+        <v>2</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="13">
-        <v>27</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G16" s="13">
-        <v>14</v>
-      </c>
-      <c r="H16" s="13" t="str">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4</v>
+      </c>
+      <c r="H16" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F16,"&lt;",G16,"&gt;"" LOC = ",$C16," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;14&gt;" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I16" s="13">
-        <v>14</v>
+        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4</v>
       </c>
       <c r="J16" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F16,"&lt;",I16,"&gt;"" LOC = ",$C16," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;14&gt;" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="L16" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,K16,""" LOC = ",$C16," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "WE" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="K16" s="1">
+        <v>4</v>
+      </c>
+      <c r="L16" s="1" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$F16,"&lt;",K16,"&gt;"" LOC = ",$C16," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -4990,40 +4990,40 @@
         <v>238</v>
       </c>
       <c r="B17" s="10">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" s="13">
-        <v>1</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G17" s="13">
-        <v>15</v>
-      </c>
-      <c r="H17" s="13" t="str">
+        <v>200</v>
+      </c>
+      <c r="E17" s="1">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F17,"&lt;",G17,"&gt;"" LOC = ",$C17," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;15&gt;" LOC = P33 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="J17" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,I17,""" LOC = ",$C17," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "VPP" LOC = P33 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="K17" s="13">
-        <v>14</v>
-      </c>
-      <c r="L17" s="13" t="str">
+        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$F17,"&lt;",I17,"&gt;"" LOC = ",$C17," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="K17" s="1">
+        <v>5</v>
+      </c>
+      <c r="L17" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F17,"&lt;",K17,"&gt;"" LOC = ",$C17," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "A&lt;14&gt;" LOC = P33 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -5031,40 +5031,40 @@
         <v>238</v>
       </c>
       <c r="B18" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E18" s="1">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>295</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H18" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F18,"&lt;",G18,"&gt;"" LOC = ",$C18," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J18" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F18,"&lt;",I18,"&gt;"" LOC = ",$C18," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F18,"&lt;",K18,"&gt;"" LOC = ",$C18," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -5072,40 +5072,40 @@
         <v>238</v>
       </c>
       <c r="B19" s="10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E19" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>295</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H19" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F19,"&lt;",G19,"&gt;"" LOC = ",$C19," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J19" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F19,"&lt;",I19,"&gt;"" LOC = ",$C19," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K19" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L19" s="1" t="str">
-        <f t="shared" ref="L19:L25" si="1" xml:space="preserve"> CONCATENATE("NET """,$F19,"&lt;",K19,"&gt;"" LOC = ",$C19," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F19,"&lt;",K19,"&gt;"" LOC = ",$C19," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -5113,40 +5113,38 @@
         <v>238</v>
       </c>
       <c r="B20" s="10">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1">
-        <v>13</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
-      </c>
-      <c r="H20" s="1" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$F20,"&lt;",G20,"&gt;"" LOC = ",$C20," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I20" s="1">
-        <v>2</v>
-      </c>
-      <c r="J20" s="1" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$F20,"&lt;",I20,"&gt;"" LOC = ",$C20," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="K20" s="1">
-        <v>2</v>
-      </c>
-      <c r="L20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;</v>
+        <v>188</v>
+      </c>
+      <c r="E20" s="13">
+        <v>20</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="H20" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$G20,""" LOC = ",$C20," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "CE" LOC = P9 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="J20" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$I20,""" LOC = ",$C20," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "CE" LOC = P9 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="L20" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,K20,""" LOC = ",$C20," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "CE" LOC = P9 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -5154,40 +5152,40 @@
         <v>238</v>
       </c>
       <c r="B21" s="10">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="E21" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="G21" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H21" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F21,"&lt;",G21,"&gt;"" LOC = ",$C21," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I21" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J21" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F21,"&lt;",I21,"&gt;"" LOC = ",$C21," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K21" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F21,"&lt;",K21,"&gt;"" LOC = ",$C21," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -5195,40 +5193,38 @@
         <v>238</v>
       </c>
       <c r="B22" s="10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>16</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="G22" s="1">
-        <v>4</v>
-      </c>
-      <c r="H22" s="1" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$F22,"&lt;",G22,"&gt;"" LOC = ",$C22," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I22" s="1">
-        <v>4</v>
-      </c>
-      <c r="J22" s="1" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$F22,"&lt;",I22,"&gt;"" LOC = ",$C22," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="K22" s="1">
-        <v>4</v>
-      </c>
-      <c r="L22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;</v>
+        <v>180</v>
+      </c>
+      <c r="E22" s="13">
+        <v>22</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="H22" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$G22,""" LOC = ",$C22," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "OE" LOC = P14 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="J22" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$I22,""" LOC = ",$C22," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "OE" LOC = P14 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L22" s="13" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,K22,""" LOC = ",$C22," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "OE" LOC = P14 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -5236,40 +5232,40 @@
         <v>238</v>
       </c>
       <c r="B23" s="10">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E23" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="G23" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H23" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F23,"&lt;",G23,"&gt;"" LOC = ",$C23," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I23" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J23" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F23,"&lt;",I23,"&gt;"" LOC = ",$C23," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K23" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F23,"&lt;",K23,"&gt;"" LOC = ",$C23," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -5277,40 +5273,40 @@
         <v>238</v>
       </c>
       <c r="B24" s="10">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="E24" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="G24" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H24" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F24,"&lt;",G24,"&gt;"" LOC = ",$C24," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I24" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J24" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F24,"&lt;",I24,"&gt;"" LOC = ",$C24," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K24" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F24,"&lt;",K24,"&gt;"" LOC = ",$C24," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -5318,40 +5314,40 @@
         <v>238</v>
       </c>
       <c r="B25" s="10">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="E25" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="G25" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F25,"&lt;",G25,"&gt;"" LOC = ",$C25," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="I25" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J25" s="1" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$F25,"&lt;",I25,"&gt;"" LOC = ",$C25," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K25" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F25,"&lt;",K25,"&gt;"" LOC = ",$C25," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -5359,38 +5355,40 @@
         <v>238</v>
       </c>
       <c r="B26" s="10">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" s="13">
-        <v>20</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="H26" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$G26,""" LOC = ",$C26," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "CE" LOC = P9 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="J26" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$I26,""" LOC = ",$C26," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "CE" LOC = P9 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="L26" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,K26,""" LOC = ",$C26," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "CE" LOC = P9 | IOSTANDARD = LVCMOS33;</v>
+        <v>164</v>
+      </c>
+      <c r="E26" s="1">
+        <v>26</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" s="1">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$F26,"&lt;",G26,"&gt;"" LOC = ",$C26," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I26" s="1">
+        <v>13</v>
+      </c>
+      <c r="J26" s="1" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$F26,"&lt;",I26,"&gt;"" LOC = ",$C26," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="K26" s="1">
+        <v>13</v>
+      </c>
+      <c r="L26" s="1" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$F26,"&lt;",K26,"&gt;"" LOC = ",$C26," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -5398,38 +5396,40 @@
         <v>238</v>
       </c>
       <c r="B27" s="10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="E27" s="13">
-        <v>22</v>
-      </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13" t="s">
-        <v>293</v>
+        <v>27</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="G27" s="13">
+        <v>14</v>
       </c>
       <c r="H27" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$G27,""" LOC = ",$C27," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "OE" LOC = P14 | IOSTANDARD = LVCMOS33;</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="J27" s="13" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,$I27,""" LOC = ",$C27," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "OE" LOC = P14 | IOSTANDARD = LVCMOS33;</v>
+        <f xml:space="preserve"> CONCATENATE("NET """,$F27,"&lt;",G27,"&gt;"" LOC = ",$C27," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;14&gt;" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
+      </c>
+      <c r="I27" s="13">
+        <v>14</v>
+      </c>
+      <c r="J27" s="1" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$F27,"&lt;",I27,"&gt;"" LOC = ",$C27," | IOSTANDARD = LVCMOS33;")</f>
+        <v>NET "A&lt;14&gt;" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L27" s="13" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,K27,""" LOC = ",$C27," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "OE" LOC = P14 | IOSTANDARD = LVCMOS33;</v>
+        <v>NET "WE" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -5451,8 +5451,8 @@
       <c r="L33" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:G31">
-    <sortCondition ref="G2:G31"/>
+  <sortState ref="A2:L33">
+    <sortCondition ref="E2:E33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/MOJO_FPGA_pinout.xlsx
+++ b/docs/MOJO_FPGA_pinout.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33060" windowHeight="17085"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33060" windowHeight="17085" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Nach FPGA Pin" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="282">
   <si>
     <t>P144</t>
   </si>
@@ -763,30 +763,9 @@
     <t>A</t>
   </si>
   <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>OE</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
-    <t>WE</t>
-  </si>
-  <si>
-    <t># EPROM 27512 UCF</t>
-  </si>
-  <si>
-    <t># RAM 62256 UCF</t>
-  </si>
-  <si>
-    <t># EPROM 27256 UCF</t>
-  </si>
-  <si>
-    <t>VPP</t>
-  </si>
-  <si>
     <t>IO_L64P_2</t>
   </si>
   <si>
@@ -835,27 +814,9 @@
     <t>27512</t>
   </si>
   <si>
-    <t>27256</t>
-  </si>
-  <si>
-    <t>62256</t>
-  </si>
-  <si>
     <t>Typ</t>
   </si>
   <si>
-    <t>IO_L37N_0 PULLUP</t>
-  </si>
-  <si>
-    <t>IO_L37P_0 PULLUP</t>
-  </si>
-  <si>
-    <t>Pullup/Pulldown Pins for unused signals</t>
-  </si>
-  <si>
-    <t>IO_L36N_GCLK14_0 PULLDOWN</t>
-  </si>
-  <si>
     <t>LED 2</t>
   </si>
   <si>
@@ -887,6 +848,30 @@
   </si>
   <si>
     <t>VCC3</t>
+  </si>
+  <si>
+    <t>PIN_22</t>
+  </si>
+  <si>
+    <t>PIN_20</t>
+  </si>
+  <si>
+    <t>PIN_27</t>
+  </si>
+  <si>
+    <t>PIN_1</t>
+  </si>
+  <si>
+    <t>PIN_26</t>
+  </si>
+  <si>
+    <t>PIN_2</t>
+  </si>
+  <si>
+    <t>PIN_23</t>
+  </si>
+  <si>
+    <t># EPROM 2716..27512 UCF</t>
   </si>
 </sst>
 </file>
@@ -969,18 +954,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1025,12 +1004,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1038,33 +1017,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1081,8 +1059,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1103,34 +1081,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1421,14 +1381,14 @@
   <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" style="23" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="22" customWidth="1"/>
     <col min="2" max="3" width="7.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>259</v>
+      <c r="A1" s="21" t="s">
+        <v>252</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>217</v>
@@ -1441,7 +1401,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="23">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1455,7 +1415,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="23">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1469,7 +1429,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="23">
+      <c r="A4" s="22">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1483,7 +1443,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1497,7 +1457,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="23">
+      <c r="A6" s="22">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1511,7 +1471,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1525,7 +1485,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="23">
+      <c r="A8" s="22">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1539,7 +1499,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="23">
+      <c r="A9" s="22">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1553,7 +1513,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+      <c r="A10" s="22">
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1567,7 +1527,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="23">
+      <c r="A11" s="22">
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1581,7 +1541,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1595,7 +1555,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
+      <c r="A13" s="22">
         <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1609,7 +1569,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="22">
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1623,7 +1583,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
+      <c r="A15" s="22">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1637,7 +1597,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+      <c r="A16" s="22">
         <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1651,7 +1611,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+      <c r="A17" s="22">
         <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1665,7 +1625,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="A18" s="22">
         <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1679,7 +1639,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="23">
+      <c r="A19" s="22">
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1693,7 +1653,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
+      <c r="A20" s="22">
         <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1707,7 +1667,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
+      <c r="A21" s="22">
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1721,7 +1681,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+      <c r="A22" s="22">
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1735,7 +1695,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="23">
+      <c r="A23" s="22">
         <v>30</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1749,7 +1709,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="23">
+      <c r="A24" s="22">
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1763,7 +1723,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="23">
+      <c r="A25" s="22">
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1774,7 +1734,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="23">
+      <c r="A26" s="22">
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1788,7 +1748,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="23">
+      <c r="A27" s="22">
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1799,7 +1759,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="23">
+      <c r="A28" s="22">
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1813,7 +1773,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="23">
+      <c r="A29" s="22">
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1827,16 +1787,16 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="23">
+      <c r="A30" s="22">
         <v>37</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>230</v>
       </c>
       <c r="D30" t="s">
         <v>198</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="25" t="s">
         <v>230</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -1844,36 +1804,36 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="23">
+      <c r="A31" s="22">
         <v>38</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="9">
+      <c r="B31" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="8">
         <v>49</v>
       </c>
       <c r="D31" t="s">
         <v>197</v>
       </c>
-      <c r="E31" s="26" t="s">
-        <v>285</v>
+      <c r="E31" s="25" t="s">
+        <v>272</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="23">
+      <c r="A32" s="22">
         <v>39</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>229</v>
       </c>
       <c r="D32" t="s">
         <v>196</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E32" s="25" t="s">
         <v>229</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -1881,7 +1841,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="23">
+      <c r="A33" s="22">
         <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -1896,7 +1856,7 @@
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="23">
+      <c r="A34" s="22">
         <v>41</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -1911,16 +1871,16 @@
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="23">
+      <c r="A35" s="22">
         <v>43</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>231</v>
       </c>
       <c r="D35" t="s">
         <v>195</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E35" s="25" t="s">
         <v>231</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -1928,16 +1888,16 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="23">
+      <c r="A36" s="22">
         <v>44</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>228</v>
       </c>
       <c r="D36" t="s">
         <v>194</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="E36" s="25" t="s">
         <v>228</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -1945,16 +1905,16 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="23">
+      <c r="A37" s="22">
         <v>45</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D37" t="s">
         <v>193</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="25" t="s">
         <v>227</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -1962,16 +1922,16 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="23">
+      <c r="A38" s="22">
         <v>46</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>226</v>
       </c>
       <c r="D38" t="s">
         <v>192</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="25" t="s">
         <v>226</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -1979,30 +1939,30 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="23">
+      <c r="A39" s="22">
         <v>47</v>
       </c>
       <c r="D39" t="s">
         <v>191</v>
       </c>
-      <c r="E39" s="41" t="s">
-        <v>262</v>
+      <c r="E39" s="33" t="s">
+        <v>255</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="23">
+      <c r="A40" s="22">
         <v>48</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>225</v>
       </c>
       <c r="D40" t="s">
         <v>190</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E40" s="25" t="s">
         <v>225</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -2010,7 +1970,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="23">
+      <c r="A41" s="22">
         <v>50</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -2019,12 +1979,12 @@
       <c r="C41" s="2">
         <v>6</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>260</v>
+      <c r="D41" s="6" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="23">
+      <c r="A42" s="22">
         <v>51</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -2033,30 +1993,30 @@
       <c r="C42" s="2">
         <v>5</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>261</v>
+      <c r="D42" s="6" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="23">
+      <c r="A43" s="22">
         <v>55</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="6" t="s">
         <v>120</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="23">
+      <c r="A44" s="22">
         <v>56</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="6" t="s">
         <v>119</v>
       </c>
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="23">
+      <c r="A45" s="22">
         <v>57</v>
       </c>
       <c r="D45" t="s">
@@ -2065,21 +2025,21 @@
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="23">
+      <c r="A46" s="22">
         <v>57</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" s="9">
+      <c r="B46" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="8">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+      <c r="A47" s="22">
         <v>58</v>
       </c>
       <c r="D47" t="s">
@@ -2088,21 +2048,21 @@
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="23">
+      <c r="A48" s="22">
         <v>58</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C48" s="9">
+      <c r="B48" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" s="8">
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="23">
+      <c r="A49" s="22">
         <v>59</v>
       </c>
       <c r="D49" t="s">
@@ -2111,30 +2071,30 @@
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="23">
+      <c r="A50" s="22">
         <v>60</v>
       </c>
       <c r="D50" t="s">
         <v>189</v>
       </c>
-      <c r="E50" s="42" t="s">
-        <v>286</v>
+      <c r="E50" s="34" t="s">
+        <v>273</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="23">
+      <c r="A51" s="22">
         <v>61</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="15" t="s">
         <v>224</v>
       </c>
       <c r="D51" t="s">
         <v>188</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E51" s="25" t="s">
         <v>224</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -2142,16 +2102,16 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="23">
+      <c r="A52" s="22">
         <v>62</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="15" t="s">
         <v>223</v>
       </c>
       <c r="D52" t="s">
         <v>187</v>
       </c>
-      <c r="E52" s="26" t="s">
+      <c r="E52" s="25" t="s">
         <v>223</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -2159,30 +2119,30 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="23">
+      <c r="A53" s="22">
         <v>64</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
       </c>
-      <c r="E53" s="41" t="s">
-        <v>262</v>
+      <c r="E53" s="33" t="s">
+        <v>255</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="23">
+      <c r="A54" s="22">
         <v>65</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="15" t="s">
         <v>222</v>
       </c>
       <c r="D54" t="s">
         <v>185</v>
       </c>
-      <c r="E54" s="26" t="s">
+      <c r="E54" s="25" t="s">
         <v>222</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -2190,13 +2150,13 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="23">
+      <c r="A55" s="22">
         <v>66</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C55" s="9">
+      <c r="B55" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C55" s="8">
         <v>10</v>
       </c>
       <c r="D55" t="s">
@@ -2205,13 +2165,13 @@
       <c r="F55" s="1"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="23">
+      <c r="A56" s="22">
         <v>67</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C56" s="9">
+      <c r="B56" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="8">
         <v>9</v>
       </c>
       <c r="D56" t="s">
@@ -2220,30 +2180,30 @@
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="23">
+      <c r="A57" s="22">
         <v>69</v>
       </c>
       <c r="D57" t="s">
         <v>184</v>
       </c>
-      <c r="E57" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="F57" s="15" t="s">
+      <c r="E57" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F57" s="14" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="23">
+      <c r="A58" s="22">
         <v>70</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="16" t="s">
         <v>232</v>
       </c>
       <c r="D58" t="s">
         <v>183</v>
       </c>
-      <c r="E58" s="26" t="s">
+      <c r="E58" s="25" t="s">
         <v>232</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -2251,24 +2211,24 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="23">
+      <c r="A59" s="22">
         <v>71</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C59" s="9">
+      <c r="B59" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C59" s="8">
         <v>6</v>
       </c>
       <c r="D59" t="s">
         <v>182</v>
       </c>
-      <c r="F59" s="15" t="s">
+      <c r="F59" s="14" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="23">
+      <c r="A60" s="22">
         <v>72</v>
       </c>
       <c r="D60" t="s">
@@ -2277,13 +2237,13 @@
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="23">
+      <c r="A61" s="22">
         <v>73</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C61" s="9">
+      <c r="B61" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="8">
         <v>5</v>
       </c>
       <c r="D61" t="s">
@@ -2292,13 +2252,13 @@
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="23">
+      <c r="A62" s="22">
         <v>74</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C62" s="9">
+      <c r="B62" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" s="8">
         <v>12</v>
       </c>
       <c r="D62" t="s">
@@ -2309,13 +2269,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="23">
+      <c r="A63" s="22">
         <v>75</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C63" s="9">
+      <c r="B63" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C63" s="8">
         <v>11</v>
       </c>
       <c r="D63" t="s">
@@ -2323,13 +2283,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="23">
+      <c r="A64" s="22">
         <v>78</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C64" s="9">
+      <c r="B64" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C64" s="8">
         <v>14</v>
       </c>
       <c r="D64" t="s">
@@ -2337,13 +2297,13 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="23">
+      <c r="A65" s="22">
         <v>79</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C65" s="9">
+      <c r="B65" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C65" s="8">
         <v>13</v>
       </c>
       <c r="D65" t="s">
@@ -2351,13 +2311,13 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="23">
+      <c r="A66" s="22">
         <v>80</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C66" s="9">
+      <c r="B66" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C66" s="8">
         <v>16</v>
       </c>
       <c r="D66" t="s">
@@ -2365,13 +2325,13 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="23">
+      <c r="A67" s="22">
         <v>81</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C67" s="9">
+      <c r="B67" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" s="8">
         <v>15</v>
       </c>
       <c r="D67" t="s">
@@ -2379,13 +2339,13 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="23">
+      <c r="A68" s="22">
         <v>82</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C68" s="9">
+      <c r="B68" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" s="8">
         <v>19</v>
       </c>
       <c r="D68" t="s">
@@ -2393,13 +2353,13 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="23">
+      <c r="A69" s="22">
         <v>83</v>
       </c>
-      <c r="B69" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C69" s="9">
+      <c r="B69" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C69" s="8">
         <v>17</v>
       </c>
       <c r="D69" t="s">
@@ -2407,125 +2367,125 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="23">
+      <c r="A70" s="22">
         <v>84</v>
       </c>
-      <c r="B70" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C70" s="9">
+      <c r="B70" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C70" s="8">
         <v>20</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="23">
+      <c r="A71" s="22">
         <v>85</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C71" s="9">
+      <c r="B71" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C71" s="8">
         <v>19</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="23">
+      <c r="A72" s="22">
         <v>87</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C72" s="9">
+      <c r="B72" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C72" s="8">
         <v>22</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="23">
+      <c r="A73" s="22">
         <v>88</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C73" s="9">
+      <c r="B73" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C73" s="8">
         <v>21</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="23">
+      <c r="A74" s="22">
         <v>92</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C74" s="9">
+      <c r="B74" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" s="8">
         <v>24</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="23">
+      <c r="A75" s="22">
         <v>93</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C75" s="9">
+      <c r="B75" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C75" s="8">
         <v>23</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="23">
+      <c r="A76" s="22">
         <v>94</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C76" s="9">
+      <c r="B76" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C76" s="8">
         <v>26</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="23">
+      <c r="A77" s="22">
         <v>95</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C77" s="9">
+      <c r="B77" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C77" s="8">
         <v>25</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="23">
+      <c r="A78" s="22">
         <v>97</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C78" s="9">
+      <c r="B78" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C78" s="8">
         <v>28</v>
       </c>
       <c r="D78" t="s">
@@ -2533,13 +2493,13 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="23">
+      <c r="A79" s="22">
         <v>98</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C79" s="9">
+      <c r="B79" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C79" s="8">
         <v>27</v>
       </c>
       <c r="D79" t="s">
@@ -2547,13 +2507,13 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="23">
+      <c r="A80" s="22">
         <v>99</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C80" s="9">
+      <c r="B80" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C80" s="8">
         <v>30</v>
       </c>
       <c r="D80" t="s">
@@ -2561,13 +2521,13 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="23">
+      <c r="A81" s="22">
         <v>100</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C81" s="9">
+      <c r="B81" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C81" s="8">
         <v>29</v>
       </c>
       <c r="D81" t="s">
@@ -2575,13 +2535,13 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="23">
+      <c r="A82" s="22">
         <v>101</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C82" s="9">
+      <c r="B82" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="8">
         <v>32</v>
       </c>
       <c r="D82" t="s">
@@ -2589,13 +2549,13 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="23">
+      <c r="A83" s="22">
         <v>102</v>
       </c>
-      <c r="B83" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C83" s="9">
+      <c r="B83" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" s="8">
         <v>31</v>
       </c>
       <c r="D83" t="s">
@@ -2603,13 +2563,13 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="23">
+      <c r="A84" s="22">
         <v>104</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C84" s="9">
+      <c r="B84" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C84" s="8">
         <v>34</v>
       </c>
       <c r="D84" t="s">
@@ -2617,13 +2577,13 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="23">
+      <c r="A85" s="22">
         <v>105</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C85" s="9">
+      <c r="B85" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C85" s="8">
         <v>33</v>
       </c>
       <c r="D85" t="s">
@@ -2631,69 +2591,69 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="23">
+      <c r="A86" s="22">
         <v>106</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C86" s="9">
+      <c r="B86" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C86" s="8">
         <v>46</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="23">
+      <c r="A87" s="22">
         <v>107</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C87" s="9">
+      <c r="B87" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C87" s="8">
         <v>45</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="7" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="23">
+      <c r="A88" s="22">
         <v>109</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C88" s="9">
+      <c r="B88" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C88" s="8">
         <v>48</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="D88" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="23">
+      <c r="A89" s="22">
         <v>110</v>
       </c>
-      <c r="B89" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C89" s="9">
+      <c r="B89" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C89" s="8">
         <v>47</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="23">
+      <c r="A90" s="22">
         <v>111</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C90" s="9">
+      <c r="B90" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C90" s="8">
         <v>36</v>
       </c>
       <c r="D90" t="s">
@@ -2701,13 +2661,13 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="23">
+      <c r="A91" s="22">
         <v>112</v>
       </c>
-      <c r="B91" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C91" s="9">
+      <c r="B91" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C91" s="8">
         <v>35</v>
       </c>
       <c r="D91" t="s">
@@ -2715,13 +2675,13 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="23">
+      <c r="A92" s="22">
         <v>114</v>
       </c>
-      <c r="B92" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C92" s="9">
+      <c r="B92" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C92" s="8">
         <v>38</v>
       </c>
       <c r="D92" t="s">
@@ -2729,13 +2689,13 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="23">
+      <c r="A93" s="22">
         <v>115</v>
       </c>
-      <c r="B93" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C93" s="9">
+      <c r="B93" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" s="8">
         <v>37</v>
       </c>
       <c r="D93" t="s">
@@ -2743,13 +2703,13 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="23">
+      <c r="A94" s="22">
         <v>116</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C94" s="9">
+      <c r="B94" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C94" s="8">
         <v>40</v>
       </c>
       <c r="D94" t="s">
@@ -2757,13 +2717,13 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="23">
+      <c r="A95" s="22">
         <v>117</v>
       </c>
-      <c r="B95" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C95" s="9">
+      <c r="B95" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C95" s="8">
         <v>39</v>
       </c>
       <c r="D95" t="s">
@@ -2771,13 +2731,13 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="23">
+      <c r="A96" s="22">
         <v>118</v>
       </c>
-      <c r="B96" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C96" s="9">
+      <c r="B96" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C96" s="8">
         <v>42</v>
       </c>
       <c r="D96" t="s">
@@ -2785,13 +2745,13 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="23">
+      <c r="A97" s="22">
         <v>119</v>
       </c>
-      <c r="B97" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C97" s="9">
+      <c r="B97" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C97" s="8">
         <v>41</v>
       </c>
       <c r="D97" t="s">
@@ -2799,13 +2759,13 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="23">
+      <c r="A98" s="22">
         <v>120</v>
       </c>
-      <c r="B98" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="9">
+      <c r="B98" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C98" s="8">
         <v>44</v>
       </c>
       <c r="D98" t="s">
@@ -2813,13 +2773,13 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="23">
+      <c r="A99" s="22">
         <v>121</v>
       </c>
-      <c r="B99" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C99" s="9">
+      <c r="B99" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C99" s="8">
         <v>43</v>
       </c>
       <c r="D99" t="s">
@@ -2827,7 +2787,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="23">
+      <c r="A100" s="22">
         <v>123</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -2836,15 +2796,15 @@
       <c r="C100" s="2">
         <v>50</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E100" s="40" t="s">
-        <v>283</v>
+      <c r="E100" s="32" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="23">
+      <c r="A101" s="22">
         <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -2853,15 +2813,15 @@
       <c r="C101" s="2">
         <v>49</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E101" s="40" t="s">
-        <v>282</v>
+      <c r="E101" s="32" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="23">
+      <c r="A102" s="22">
         <v>126</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -2870,15 +2830,15 @@
       <c r="C102" s="2">
         <v>48</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E102" s="40" t="s">
-        <v>281</v>
+      <c r="E102" s="32" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="23">
+      <c r="A103" s="22">
         <v>127</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -2887,15 +2847,15 @@
       <c r="C103" s="2">
         <v>47</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E103" s="40" t="s">
-        <v>280</v>
+      <c r="E103" s="32" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="23">
+      <c r="A104" s="22">
         <v>131</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -2904,15 +2864,15 @@
       <c r="C104" s="2">
         <v>46</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E104" s="40" t="s">
-        <v>279</v>
+      <c r="E104" s="32" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="23">
+      <c r="A105" s="22">
         <v>132</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -2921,15 +2881,15 @@
       <c r="C105" s="2">
         <v>45</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E105" s="40" t="s">
-        <v>278</v>
+      <c r="E105" s="32" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="23">
+      <c r="A106" s="22">
         <v>133</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -2938,15 +2898,15 @@
       <c r="C106" s="2">
         <v>44</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E106" s="40" t="s">
-        <v>277</v>
+      <c r="E106" s="32" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="23">
+      <c r="A107" s="22">
         <v>134</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -2955,15 +2915,15 @@
       <c r="C107" s="2">
         <v>43</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E107" s="40" t="s">
-        <v>276</v>
+      <c r="E107" s="32" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="23">
+      <c r="A108" s="22">
         <v>137</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -2977,7 +2937,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="23">
+      <c r="A109" s="22">
         <v>138</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -2991,7 +2951,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="23">
+      <c r="A110" s="22">
         <v>139</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -3005,7 +2965,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="23">
+      <c r="A111" s="22">
         <v>140</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -3019,7 +2979,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="23">
+      <c r="A112" s="22">
         <v>141</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -3033,7 +2993,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="23">
+      <c r="A113" s="22">
         <v>142</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -3047,7 +3007,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="23">
+      <c r="A114" s="22">
         <v>143</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -3061,7 +3021,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="23">
+      <c r="A115" s="22">
         <v>144</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -3114,69 +3074,69 @@
         <v>233</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B2" s="11">
+      <c r="A2" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="24" t="s">
-        <v>262</v>
+      <c r="C2" s="12"/>
+      <c r="D2" s="23" t="s">
+        <v>255</v>
       </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="A3" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="24" t="s">
-        <v>263</v>
+      <c r="C3" s="12"/>
+      <c r="D3" s="23" t="s">
+        <v>256</v>
       </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="A4" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="10">
         <v>3</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="24" t="s">
-        <v>262</v>
+      <c r="C4" s="12"/>
+      <c r="D4" s="23" t="s">
+        <v>255</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="11">
+      <c r="A5" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="10">
         <v>4</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="24" t="s">
-        <v>264</v>
+      <c r="C5" s="12"/>
+      <c r="D5" s="23" t="s">
+        <v>257</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="10">
         <v>5</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>107</v>
       </c>
       <c r="D6" t="s">
@@ -3184,34 +3144,34 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" s="11">
+      <c r="A7" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="10">
         <v>6</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>109</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
       </c>
       <c r="F7" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="10">
         <v>7</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F8" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$A8,"_",B8,""" LOC = ",$C8," | IOSTANDARD = LVCMOS33;   # ",D8)</f>
@@ -3219,17 +3179,17 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="10">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" ref="F9:F45" si="0" xml:space="preserve"> CONCATENATE("NET """,$A9,"_",B9,""" LOC = ",$C9," | IOSTANDARD = LVCMOS33;   # ",D9)</f>
@@ -3237,13 +3197,13 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="A10" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="10">
         <v>9</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>110</v>
       </c>
       <c r="D10" t="s">
@@ -3255,13 +3215,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="11">
+      <c r="A11" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="10">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>112</v>
       </c>
       <c r="D11" t="s">
@@ -3273,13 +3233,13 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="11">
+      <c r="A12" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="10">
         <v>11</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D12" t="s">
@@ -3291,13 +3251,13 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B13" s="11">
+      <c r="A13" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="10">
         <v>12</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>106</v>
       </c>
       <c r="D13" t="s">
@@ -3309,13 +3269,13 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="11">
+      <c r="A14" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="10">
         <v>13</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>100</v>
       </c>
       <c r="D14" t="s">
@@ -3327,13 +3287,13 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B15" s="11">
+      <c r="A15" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="10">
         <v>14</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D15" t="s">
@@ -3345,13 +3305,13 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B16" s="11">
+      <c r="A16" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="10">
         <v>15</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>96</v>
       </c>
       <c r="D16" t="s">
@@ -3363,13 +3323,13 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B17" s="11">
+      <c r="A17" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" s="10">
         <v>16</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>98</v>
       </c>
       <c r="D17" t="s">
@@ -3381,13 +3341,13 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B18" s="11">
+      <c r="A18" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="10">
         <v>17</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>92</v>
       </c>
       <c r="D18" t="s">
@@ -3399,16 +3359,16 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B19" s="11">
+      <c r="A19" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="10">
         <v>19</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>89</v>
       </c>
       <c r="F19" t="str">
@@ -3417,13 +3377,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B20" s="11">
+      <c r="A20" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20" s="10">
         <v>19</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>94</v>
       </c>
       <c r="D20" t="s">
@@ -3435,16 +3395,16 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B21" s="11">
+      <c r="A21" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="10">
         <v>20</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>91</v>
       </c>
       <c r="F21" t="str">
@@ -3453,16 +3413,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B22" s="11">
+      <c r="A22" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B22" s="10">
         <v>21</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="str">
@@ -3471,19 +3431,19 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="11">
+      <c r="A23" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="10">
         <v>22</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="25" t="s">
         <v>238</v>
       </c>
       <c r="F23" t="str">
@@ -3492,19 +3452,19 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B24" s="11">
+      <c r="A24" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="10">
         <v>23</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="25" t="s">
         <v>239</v>
       </c>
       <c r="F24" t="str">
@@ -3513,19 +3473,19 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B25" s="11">
+      <c r="A25" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="10">
         <v>24</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="25" t="s">
         <v>240</v>
       </c>
       <c r="F25" t="str">
@@ -3534,19 +3494,19 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="11">
+      <c r="A26" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="10">
         <v>25</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="25" t="s">
         <v>241</v>
       </c>
       <c r="F26" t="str">
@@ -3555,19 +3515,19 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="11">
+      <c r="A27" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B27" s="10">
         <v>26</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="25" t="s">
         <v>242</v>
       </c>
       <c r="F27" t="str">
@@ -3576,13 +3536,13 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B28" s="11">
+      <c r="A28" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="10">
         <v>27</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D28" t="s">
@@ -3594,13 +3554,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B29" s="11">
+      <c r="A29" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="10">
         <v>28</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="12" t="s">
         <v>74</v>
       </c>
       <c r="D29" t="s">
@@ -3612,13 +3572,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B30" s="11">
+      <c r="A30" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B30" s="10">
         <v>29</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D30" t="s">
@@ -3630,13 +3590,13 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B31" s="11">
+      <c r="A31" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="10">
         <v>30</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="12" t="s">
         <v>70</v>
       </c>
       <c r="D31" t="s">
@@ -3648,13 +3608,13 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B32" s="11">
+      <c r="A32" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B32" s="10">
         <v>31</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>64</v>
       </c>
       <c r="D32" t="s">
@@ -3666,13 +3626,13 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="11">
+      <c r="A33" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="10">
         <v>32</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="12" t="s">
         <v>66</v>
       </c>
       <c r="D33" t="s">
@@ -3684,13 +3644,13 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B34" s="11">
+      <c r="A34" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B34" s="10">
         <v>33</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="12" t="s">
         <v>60</v>
       </c>
       <c r="D34" t="s">
@@ -3702,13 +3662,13 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B35" s="11">
+      <c r="A35" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" s="10">
         <v>34</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>62</v>
       </c>
       <c r="D35" t="s">
@@ -3720,13 +3680,13 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B36" s="11">
+      <c r="A36" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" s="10">
         <v>35</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>48</v>
       </c>
       <c r="D36" t="s">
@@ -3738,13 +3698,13 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B37" s="11">
+      <c r="A37" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B37" s="10">
         <v>36</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>50</v>
       </c>
       <c r="D37" t="s">
@@ -3756,13 +3716,13 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B38" s="11">
+      <c r="A38" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" s="10">
         <v>37</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>44</v>
       </c>
       <c r="D38" t="s">
@@ -3774,13 +3734,13 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B39" s="11">
+      <c r="A39" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="10">
         <v>38</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D39" t="s">
@@ -3792,13 +3752,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B40" s="11">
+      <c r="A40" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B40" s="10">
         <v>39</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="12" t="s">
         <v>40</v>
       </c>
       <c r="D40" t="s">
@@ -3810,13 +3770,13 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B41" s="11">
+      <c r="A41" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" s="10">
         <v>40</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="12" t="s">
         <v>42</v>
       </c>
       <c r="D41" t="s">
@@ -3828,13 +3788,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B42" s="11">
+      <c r="A42" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="10">
         <v>41</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D42" t="s">
@@ -3846,13 +3806,13 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="11">
+      <c r="A43" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="10">
         <v>42</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D43" t="s">
@@ -3864,13 +3824,13 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B44" s="11">
+      <c r="A44" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B44" s="10">
         <v>43</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D44" t="s">
@@ -3882,13 +3842,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B45" s="11">
+      <c r="A45" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="10">
         <v>44</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>34</v>
       </c>
       <c r="D45" t="s">
@@ -3900,97 +3860,100 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B46" s="11">
+      <c r="A46" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" s="10">
         <v>45</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="25" t="s">
+      <c r="D46" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E46" s="25" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B47" s="11">
+      <c r="A47" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B47" s="10">
         <v>46</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="25" t="s">
+      <c r="D47" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E47" s="26" t="s">
+      <c r="E47" s="25" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B48" s="11">
+      <c r="A48" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B48" s="10">
         <v>47</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="26" t="s">
+      <c r="E48" s="25" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B49" s="11">
+      <c r="A49" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="10">
         <v>48</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D49" s="25" t="s">
+      <c r="D49" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E49" s="26" t="s">
+      <c r="E49" s="25" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B50" s="11">
+      <c r="A50" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" s="10">
         <v>49</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="12" t="s">
         <v>126</v>
       </c>
       <c r="D50" t="s">
         <v>197</v>
       </c>
+      <c r="E50" s="25" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B51" s="11">
+      <c r="A51" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" s="10">
         <v>50</v>
       </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="24" t="s">
-        <v>262</v>
+      <c r="C51" s="12"/>
+      <c r="D51" s="23" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4004,68 +3967,68 @@
       <c r="A53" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="11">
         <v>1</v>
       </c>
-      <c r="C53" s="14"/>
-      <c r="D53" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="F53" s="10"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F53" s="9"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="11">
         <v>2</v>
       </c>
-      <c r="C54" s="14"/>
-      <c r="D54" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="F54" s="10"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F54" s="9"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="11">
         <v>3</v>
       </c>
-      <c r="C55" s="14"/>
-      <c r="D55" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="F55" s="10"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F55" s="9"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B56" s="11">
         <v>4</v>
       </c>
-      <c r="C56" s="14"/>
-      <c r="D56" s="24" t="s">
-        <v>264</v>
+      <c r="C56" s="13"/>
+      <c r="D56" s="23" t="s">
+        <v>257</v>
       </c>
       <c r="F56" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B57" s="12">
+      <c r="B57" s="11">
         <v>5</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="13" t="s">
         <v>179</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" ref="F57:F102" si="1" xml:space="preserve"> CONCATENATE("NET """,$A57,"_",B57,""" LOC = ",$C57," | IOSTANDARD = LVCMOS33;   # ",D57)</f>
@@ -4076,14 +4039,14 @@
       <c r="A58" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B58" s="11">
         <v>6</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="13" t="s">
         <v>121</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F58" t="str">
         <f t="shared" si="1"/>
@@ -4094,14 +4057,14 @@
       <c r="A59" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B59" s="12">
+      <c r="B59" s="11">
         <v>7</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="13" t="s">
         <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
@@ -4112,14 +4075,14 @@
       <c r="A60" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="11">
         <v>8</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F60" t="str">
         <f t="shared" si="1"/>
@@ -4130,10 +4093,10 @@
       <c r="A61" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B61" s="12">
+      <c r="B61" s="11">
         <v>9</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>127</v>
       </c>
       <c r="D61" t="s">
@@ -4148,10 +4111,10 @@
       <c r="A62" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="11">
         <v>10</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>129</v>
       </c>
       <c r="D62" t="s">
@@ -4166,10 +4129,10 @@
       <c r="A63" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="11">
         <v>11</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="13" t="s">
         <v>131</v>
       </c>
       <c r="D63" t="s">
@@ -4184,10 +4147,10 @@
       <c r="A64" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="11">
         <v>12</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="13" t="s">
         <v>133</v>
       </c>
       <c r="D64" t="s">
@@ -4202,10 +4165,10 @@
       <c r="A65" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="11">
         <v>13</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="13" t="s">
         <v>135</v>
       </c>
       <c r="D65" t="s">
@@ -4220,10 +4183,10 @@
       <c r="A66" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="11">
         <v>14</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="13" t="s">
         <v>137</v>
       </c>
       <c r="D66" t="s">
@@ -4238,10 +4201,10 @@
       <c r="A67" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="11">
         <v>15</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="13" t="s">
         <v>139</v>
       </c>
       <c r="D67" t="s">
@@ -4256,10 +4219,10 @@
       <c r="A68" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="11">
         <v>16</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D68" t="s">
@@ -4274,10 +4237,10 @@
       <c r="A69" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="11">
         <v>17</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>143</v>
       </c>
       <c r="D69" s="5" t="s">
@@ -4292,10 +4255,10 @@
       <c r="A70" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="11">
         <v>18</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="13" t="s">
         <v>145</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -4310,10 +4273,10 @@
       <c r="A71" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B71" s="12">
+      <c r="B71" s="11">
         <v>19</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D71" s="5" t="s">
@@ -4328,10 +4291,10 @@
       <c r="A72" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B72" s="12">
+      <c r="B72" s="11">
         <v>20</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="13" t="s">
         <v>149</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -4346,10 +4309,10 @@
       <c r="A73" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B73" s="12">
+      <c r="B73" s="11">
         <v>21</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="13" t="s">
         <v>151</v>
       </c>
       <c r="D73" s="5" t="s">
@@ -4364,10 +4327,10 @@
       <c r="A74" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B74" s="12">
+      <c r="B74" s="11">
         <v>22</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="13" t="s">
         <v>153</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -4382,10 +4345,10 @@
       <c r="A75" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B75" s="12">
+      <c r="B75" s="11">
         <v>23</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D75" s="5" t="s">
@@ -4400,10 +4363,10 @@
       <c r="A76" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B76" s="12">
+      <c r="B76" s="11">
         <v>24</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="13" t="s">
         <v>157</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -4420,10 +4383,10 @@
       <c r="A77" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B77" s="12">
+      <c r="B77" s="11">
         <v>25</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="13" t="s">
         <v>159</v>
       </c>
       <c r="D77" t="s">
@@ -4438,10 +4401,10 @@
       <c r="A78" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B78" s="12">
+      <c r="B78" s="11">
         <v>26</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="13" t="s">
         <v>161</v>
       </c>
       <c r="D78" t="s">
@@ -4456,10 +4419,10 @@
       <c r="A79" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="11">
         <v>27</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>163</v>
       </c>
       <c r="D79" t="s">
@@ -4474,10 +4437,10 @@
       <c r="A80" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="11">
         <v>28</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>165</v>
       </c>
       <c r="D80" t="s">
@@ -4494,10 +4457,10 @@
       <c r="A81" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B81" s="12">
+      <c r="B81" s="11">
         <v>29</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D81" t="s">
@@ -4512,10 +4475,10 @@
       <c r="A82" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B82" s="12">
+      <c r="B82" s="11">
         <v>30</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="13" t="s">
         <v>169</v>
       </c>
       <c r="D82" t="s">
@@ -4530,10 +4493,10 @@
       <c r="A83" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B83" s="12">
+      <c r="B83" s="11">
         <v>31</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="13" t="s">
         <v>171</v>
       </c>
       <c r="D83" t="s">
@@ -4548,10 +4511,10 @@
       <c r="A84" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B84" s="12">
+      <c r="B84" s="11">
         <v>32</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="13" t="s">
         <v>173</v>
       </c>
       <c r="D84" t="s">
@@ -4566,10 +4529,10 @@
       <c r="A85" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B85" s="12">
+      <c r="B85" s="11">
         <v>33</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="13" t="s">
         <v>175</v>
       </c>
       <c r="D85" t="s">
@@ -4584,10 +4547,10 @@
       <c r="A86" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B86" s="12">
+      <c r="B86" s="11">
         <v>34</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="13" t="s">
         <v>177</v>
       </c>
       <c r="D86" t="s">
@@ -4602,10 +4565,10 @@
       <c r="A87" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B87" s="12">
+      <c r="B87" s="11">
         <v>35</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D87" t="s">
@@ -4620,10 +4583,10 @@
       <c r="A88" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B88" s="12">
+      <c r="B88" s="11">
         <v>36</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D88" t="s">
@@ -4638,10 +4601,10 @@
       <c r="A89" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B89" s="12">
+      <c r="B89" s="11">
         <v>37</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D89" t="s">
@@ -4656,10 +4619,10 @@
       <c r="A90" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B90" s="12">
+      <c r="B90" s="11">
         <v>38</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="13" t="s">
         <v>6</v>
       </c>
       <c r="D90" t="s">
@@ -4674,10 +4637,10 @@
       <c r="A91" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B91" s="12">
+      <c r="B91" s="11">
         <v>39</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D91" t="s">
@@ -4692,10 +4655,10 @@
       <c r="A92" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B92" s="12">
+      <c r="B92" s="11">
         <v>40</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D92" t="s">
@@ -4710,10 +4673,10 @@
       <c r="A93" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B93" s="12">
+      <c r="B93" s="11">
         <v>41</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="13" t="s">
         <v>12</v>
       </c>
       <c r="D93" t="s">
@@ -4728,10 +4691,10 @@
       <c r="A94" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B94" s="12">
+      <c r="B94" s="11">
         <v>42</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D94" t="s">
@@ -4746,17 +4709,17 @@
       <c r="A95" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B95" s="12">
+      <c r="B95" s="11">
         <v>43</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="D95" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E95" s="40" t="s">
-        <v>276</v>
+      <c r="E95" s="32" t="s">
+        <v>263</v>
       </c>
       <c r="F95" t="str">
         <f t="shared" si="1"/>
@@ -4767,17 +4730,17 @@
       <c r="A96" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B96" s="12">
+      <c r="B96" s="11">
         <v>44</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E96" s="40" t="s">
-        <v>277</v>
+      <c r="E96" s="32" t="s">
+        <v>264</v>
       </c>
       <c r="F96" t="str">
         <f t="shared" si="1"/>
@@ -4788,17 +4751,17 @@
       <c r="A97" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B97" s="12">
+      <c r="B97" s="11">
         <v>45</v>
       </c>
-      <c r="C97" s="14" t="s">
+      <c r="C97" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E97" s="40" t="s">
-        <v>278</v>
+      <c r="E97" s="32" t="s">
+        <v>265</v>
       </c>
       <c r="F97" t="str">
         <f t="shared" si="1"/>
@@ -4809,17 +4772,17 @@
       <c r="A98" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="12">
+      <c r="B98" s="11">
         <v>46</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E98" s="40" t="s">
-        <v>279</v>
+      <c r="E98" s="32" t="s">
+        <v>266</v>
       </c>
       <c r="F98" t="str">
         <f t="shared" si="1"/>
@@ -4830,17 +4793,17 @@
       <c r="A99" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B99" s="12">
+      <c r="B99" s="11">
         <v>47</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D99" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E99" s="40" t="s">
-        <v>280</v>
+      <c r="E99" s="32" t="s">
+        <v>267</v>
       </c>
       <c r="F99" t="str">
         <f t="shared" si="1"/>
@@ -4851,17 +4814,17 @@
       <c r="A100" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B100" s="12">
+      <c r="B100" s="11">
         <v>48</v>
       </c>
-      <c r="C100" s="14" t="s">
+      <c r="C100" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E100" s="40" t="s">
-        <v>281</v>
+      <c r="E100" s="32" t="s">
+        <v>268</v>
       </c>
       <c r="F100" t="str">
         <f t="shared" si="1"/>
@@ -4872,17 +4835,17 @@
       <c r="A101" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B101" s="12">
+      <c r="B101" s="11">
         <v>49</v>
       </c>
-      <c r="C101" s="14" t="s">
+      <c r="C101" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E101" s="40" t="s">
-        <v>282</v>
+      <c r="E101" s="32" t="s">
+        <v>269</v>
       </c>
       <c r="F101" t="str">
         <f t="shared" si="1"/>
@@ -4893,17 +4856,17 @@
       <c r="A102" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B102" s="12">
+      <c r="B102" s="11">
         <v>50</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E102" s="40" t="s">
-        <v>283</v>
+      <c r="E102" s="32" t="s">
+        <v>270</v>
       </c>
       <c r="F102" t="str">
         <f t="shared" si="1"/>
@@ -4911,16 +4874,16 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D110" s="7"/>
+      <c r="D110" s="6"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D111" s="7"/>
+      <c r="D111" s="6"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D112" s="7"/>
+      <c r="D112" s="6"/>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D113" s="7"/>
+      <c r="D113" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -4930,20 +4893,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="11.42578125" style="1"/>
-    <col min="4" max="4" width="27.140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" style="20" customWidth="1"/>
     <col min="5" max="5" width="10.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="3.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" style="28" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" customWidth="1"/>
     <col min="9" max="9" width="80.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" style="29" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="28" customWidth="1"/>
     <col min="11" max="11" width="7" style="1" customWidth="1"/>
     <col min="12" max="12" width="72.28515625" customWidth="1"/>
-    <col min="13" max="13" width="4.5703125" style="29" customWidth="1"/>
+    <col min="13" max="13" width="4.5703125" style="28" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="82.7109375" customWidth="1"/>
     <col min="16" max="16384" width="11.42578125" style="1"/>
@@ -4959,1390 +4922,1041 @@
       <c r="C1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>268</v>
+      <c r="F1" s="18"/>
+      <c r="G1" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>261</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="K1" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="N1" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>250</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="J1" s="27"/>
+      <c r="K1" s="26"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="26"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="12">
-        <v>13</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>136</v>
+      <c r="B2" s="11">
+        <v>15</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="E2" s="1">
-        <v>2</v>
-      </c>
-      <c r="G2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H2" s="4">
-        <v>12</v>
-      </c>
-      <c r="I2" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,G2,"&lt;",H2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;  # ",$D2,", ",$A2," Pin ",$B2)</f>
-        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;  # IO_L36P_3 , SV2 Pin 13</v>
-      </c>
-      <c r="J2" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K2" s="4">
-        <v>12</v>
-      </c>
-      <c r="L2" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,J2,"&lt;",K2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;  # ",$D2,", ",$A2," Pin ",$B2)</f>
-        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;  # IO_L36P_3 , SV2 Pin 13</v>
-      </c>
-      <c r="M2" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N2" s="4">
-        <v>12</v>
-      </c>
-      <c r="O2" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,M2,"&lt;",N2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;  # ",$D2,", ",$A2," Pin ",$B2)</f>
-        <v>NET "A&lt;12&gt;" LOC = P30 | IOSTANDARD = LVCMOS33;  # IO_L36P_3 , SV2 Pin 13</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="I2" s="20" t="str">
+        <f t="shared" ref="I2:I20" si="0" xml:space="preserve"> CONCATENATE("NET """,G2,"&lt;",H2,"&gt;"" LOC = ",$C2," | IOSTANDARD = LVCMOS33;  # ",$D2,", ",$A2," Pin ",$B2)</f>
+        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;  # IO_L37P_3 , SV2 Pin 15</v>
+      </c>
+      <c r="J2" s="27"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="12">
-        <v>15</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>140</v>
+      <c r="B3" s="11">
+        <v>17</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="E3" s="1">
-        <v>3</v>
-      </c>
-      <c r="G3" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H3" s="4">
-        <v>7</v>
-      </c>
-      <c r="I3" s="21" t="str">
-        <f t="shared" ref="I3:I23" si="0" xml:space="preserve"> CONCATENATE("NET """,G3,"&lt;",H3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;  # ",$D3,", ",$A3," Pin ",$B3)</f>
-        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;  # IO_L37P_3 , SV2 Pin 15</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K3" s="4">
-        <v>7</v>
-      </c>
-      <c r="L3" s="21" t="str">
-        <f t="shared" ref="L3:L25" si="1" xml:space="preserve"> CONCATENATE("NET """,J3,"&lt;",K3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;  # ",$D3,", ",$A3," Pin ",$B3)</f>
-        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;  # IO_L37P_3 , SV2 Pin 15</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N3" s="4">
-        <v>7</v>
-      </c>
-      <c r="O3" s="21" t="str">
-        <f t="shared" ref="O3:O23" si="2" xml:space="preserve"> CONCATENATE("NET """,M3,"&lt;",N3,"&gt;"" LOC = ",$C3," | IOSTANDARD = LVCMOS33;  # ",$D3,", ",$A3," Pin ",$B3)</f>
-        <v>NET "A&lt;7&gt;" LOC = P27 | IOSTANDARD = LVCMOS33;  # IO_L37P_3 , SV2 Pin 15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="I3" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;  # IO_L41P_GCLK27_3 , SV2 Pin 17</v>
+      </c>
+      <c r="J3" s="27"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="20"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="12">
-        <v>17</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>144</v>
+      <c r="B4" s="11">
+        <v>19</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>148</v>
       </c>
       <c r="E4" s="1">
-        <v>4</v>
-      </c>
-      <c r="G4" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H4" s="4">
-        <v>6</v>
-      </c>
-      <c r="I4" s="21" t="str">
+        <v>5</v>
+      </c>
+      <c r="I4" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;  # IO_L41P_GCLK27_3 , SV2 Pin 17</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K4" s="4">
-        <v>6</v>
-      </c>
-      <c r="L4" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;  # IO_L41P_GCLK27_3 , SV2 Pin 17</v>
-      </c>
-      <c r="M4" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N4" s="4">
-        <v>6</v>
-      </c>
-      <c r="O4" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;6&gt;" LOC = P24 | IOSTANDARD = LVCMOS33;  # IO_L41P_GCLK27_3 , SV2 Pin 17</v>
-      </c>
+        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;  # IO_L42P_GCLK25_TRDY2_3 , SV2 Pin 19</v>
+      </c>
+      <c r="J4" s="27"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="20"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B5" s="12">
-        <v>19</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>148</v>
+      <c r="B5" s="11">
+        <v>21</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>152</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
-      </c>
-      <c r="G5" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H5" s="4">
-        <v>5</v>
-      </c>
-      <c r="I5" s="21" t="str">
+        <v>4</v>
+      </c>
+      <c r="I5" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;  # IO_L42P_GCLK25_TRDY2_3 , SV2 Pin 19</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K5" s="4">
-        <v>5</v>
-      </c>
-      <c r="L5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;  # IO_L42P_GCLK25_TRDY2_3 , SV2 Pin 19</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N5" s="4">
-        <v>5</v>
-      </c>
-      <c r="O5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;5&gt;" LOC = P22 | IOSTANDARD = LVCMOS33;  # IO_L42P_GCLK25_TRDY2_3 , SV2 Pin 19</v>
-      </c>
+        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;  # IO_L43P_GCLK23_3 , SV2 Pin 21</v>
+      </c>
+      <c r="J5" s="27"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B6" s="12">
-        <v>21</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>152</v>
+      <c r="B6" s="11">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="E6" s="1">
-        <v>6</v>
-      </c>
-      <c r="G6" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H6" s="4">
-        <v>4</v>
-      </c>
-      <c r="I6" s="21" t="str">
+        <v>3</v>
+      </c>
+      <c r="I6" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;  # IO_L43P_GCLK23_3 , SV2 Pin 21</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K6" s="4">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;  # IO_L43P_GCLK23_3 , SV2 Pin 21</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N6" s="4">
-        <v>4</v>
-      </c>
-      <c r="O6" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;4&gt;" LOC = P17 | IOSTANDARD = LVCMOS33;  # IO_L43P_GCLK23_3 , SV2 Pin 21</v>
-      </c>
+        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;  # IO_L44P_GCLK21_3 , SV2 Pin 23</v>
+      </c>
+      <c r="J6" s="27"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="20"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B7" s="12">
-        <v>23</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>156</v>
+      <c r="B7" s="11">
+        <v>25</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>160</v>
       </c>
       <c r="E7" s="1">
-        <v>7</v>
-      </c>
-      <c r="G7" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H7" s="4">
-        <v>3</v>
-      </c>
-      <c r="I7" s="21" t="str">
+        <v>2</v>
+      </c>
+      <c r="I7" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;  # IO_L44P_GCLK21_3 , SV2 Pin 23</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K7" s="4">
-        <v>3</v>
-      </c>
-      <c r="L7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;  # IO_L44P_GCLK21_3 , SV2 Pin 23</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N7" s="4">
-        <v>3</v>
-      </c>
-      <c r="O7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;3&gt;" LOC = P15 | IOSTANDARD = LVCMOS33;  # IO_L44P_GCLK21_3 , SV2 Pin 23</v>
-      </c>
+        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;  # IO_L49P_3 , SV2 Pin 25</v>
+      </c>
+      <c r="J7" s="27"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="20"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B8" s="12">
-        <v>25</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>160</v>
+      <c r="B8" s="11">
+        <v>27</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>164</v>
       </c>
       <c r="E8" s="1">
-        <v>8</v>
-      </c>
-      <c r="G8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H8" s="4">
-        <v>2</v>
-      </c>
-      <c r="I8" s="21" t="str">
+        <v>1</v>
+      </c>
+      <c r="I8" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;  # IO_L49P_3 , SV2 Pin 25</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K8" s="4">
-        <v>2</v>
-      </c>
-      <c r="L8" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;  # IO_L49P_3 , SV2 Pin 25</v>
-      </c>
-      <c r="M8" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N8" s="4">
-        <v>2</v>
-      </c>
-      <c r="O8" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;2&gt;" LOC = P12 | IOSTANDARD = LVCMOS33;  # IO_L49P_3 , SV2 Pin 25</v>
-      </c>
+        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;  # IO_L50P_3 , SV2 Pin 27</v>
+      </c>
+      <c r="J8" s="27"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="20"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B9" s="12">
-        <v>27</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>164</v>
+      <c r="B9" s="11">
+        <v>29</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>168</v>
       </c>
       <c r="E9" s="1">
-        <v>9</v>
-      </c>
-      <c r="G9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;  # IO_L50P_3 , SV2 Pin 27</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K9" s="4">
-        <v>1</v>
-      </c>
-      <c r="L9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;  # IO_L50P_3 , SV2 Pin 27</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1</v>
-      </c>
-      <c r="O9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;1&gt;" LOC = P10 | IOSTANDARD = LVCMOS33;  # IO_L50P_3 , SV2 Pin 27</v>
-      </c>
+        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;  # IO_L51P_3 , SV2 Pin 29</v>
+      </c>
+      <c r="J9" s="27"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B10" s="12">
-        <v>29</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>168</v>
+      <c r="B10" s="11">
+        <v>31</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>172</v>
       </c>
       <c r="E10" s="1">
-        <v>10</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>244</v>
+        <v>11</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="21" t="str">
+      <c r="I10" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;  # IO_L51P_3 , SV2 Pin 29</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;  # IO_L51P_3 , SV2 Pin 29</v>
-      </c>
-      <c r="M10" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="O10" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;0&gt;" LOC = P8 | IOSTANDARD = LVCMOS33;  # IO_L51P_3 , SV2 Pin 29</v>
-      </c>
+        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;  # IO_L52P_3 , SV2 Pin 31</v>
+      </c>
+      <c r="J10" s="27"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="12">
-        <v>31</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>172</v>
+      <c r="B11" s="11">
+        <v>33</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>176</v>
       </c>
       <c r="E11" s="1">
-        <v>11</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>247</v>
+        <v>12</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21" t="str">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;  # IO_L52P_3 , SV2 Pin 31</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-      <c r="L11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;  # IO_L52P_3 , SV2 Pin 31</v>
-      </c>
-      <c r="M11" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0</v>
-      </c>
-      <c r="O11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;0&gt;" LOC = P6 | IOSTANDARD = LVCMOS33;  # IO_L52P_3 , SV2 Pin 31</v>
-      </c>
+        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;  # IO_L83P_3 , SV2 Pin 33</v>
+      </c>
+      <c r="J11" s="27"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="20"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="12">
-        <v>33</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>176</v>
+      <c r="B12" s="11">
+        <v>35</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>12</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>247</v>
+        <v>13</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="21" t="str">
+        <v>2</v>
+      </c>
+      <c r="I12" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;  # IO_L83P_3 , SV2 Pin 33</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K12" s="4">
-        <v>1</v>
-      </c>
-      <c r="L12" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;  # IO_L83P_3 , SV2 Pin 33</v>
-      </c>
-      <c r="M12" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N12" s="4">
-        <v>1</v>
-      </c>
-      <c r="O12" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;1&gt;" LOC = P2 | IOSTANDARD = LVCMOS33;  # IO_L83P_3 , SV2 Pin 33</v>
-      </c>
+        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;  # IO_L1P_HSWAPEN_0 , SV2 Pin 35</v>
+      </c>
+      <c r="J12" s="27"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="20"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B13" s="12">
-        <v>35</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>1</v>
+      <c r="B13" s="11">
+        <v>38</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>7</v>
       </c>
       <c r="E13" s="1">
-        <v>13</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>247</v>
+        <v>15</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H13" s="4">
-        <v>2</v>
-      </c>
-      <c r="I13" s="21" t="str">
+        <v>3</v>
+      </c>
+      <c r="I13" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;  # IO_L1P_HSWAPEN_0 , SV2 Pin 35</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K13" s="4">
-        <v>2</v>
-      </c>
-      <c r="L13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;  # IO_L1P_HSWAPEN_0 , SV2 Pin 35</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N13" s="4">
-        <v>2</v>
-      </c>
-      <c r="O13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;2&gt;" LOC = P144 | IOSTANDARD = LVCMOS33;  # IO_L1P_HSWAPEN_0 , SV2 Pin 35</v>
-      </c>
+        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;  # IO_L2N_0 , SV2 Pin 38</v>
+      </c>
+      <c r="J13" s="27"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="20"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="12">
-        <v>38</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>7</v>
+      <c r="B14" s="11">
+        <v>36</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="1">
-        <v>15</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>247</v>
+        <v>16</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H14" s="4">
-        <v>3</v>
-      </c>
-      <c r="I14" s="21" t="str">
+        <v>4</v>
+      </c>
+      <c r="I14" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;  # IO_L2N_0 , SV2 Pin 38</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K14" s="4">
-        <v>3</v>
-      </c>
-      <c r="L14" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;  # IO_L2N_0 , SV2 Pin 38</v>
-      </c>
-      <c r="M14" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N14" s="4">
-        <v>3</v>
-      </c>
-      <c r="O14" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;3&gt;" LOC = P141 | IOSTANDARD = LVCMOS33;  # IO_L2N_0 , SV2 Pin 38</v>
-      </c>
+        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;  # IO_L1N_VREF_0 , SV2 Pin 36</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="20"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B15" s="12">
-        <v>36</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>3</v>
+      <c r="B15" s="11">
+        <v>34</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>178</v>
       </c>
       <c r="E15" s="1">
-        <v>16</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>247</v>
+        <v>17</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H15" s="4">
-        <v>4</v>
-      </c>
-      <c r="I15" s="21" t="str">
+        <v>5</v>
+      </c>
+      <c r="I15" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;  # IO_L1N_VREF_0 , SV2 Pin 36</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K15" s="4">
-        <v>4</v>
-      </c>
-      <c r="L15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;  # IO_L1N_VREF_0 , SV2 Pin 36</v>
-      </c>
-      <c r="M15" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N15" s="4">
-        <v>4</v>
-      </c>
-      <c r="O15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;4&gt;" LOC = P143 | IOSTANDARD = LVCMOS33;  # IO_L1N_VREF_0 , SV2 Pin 36</v>
-      </c>
+        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;  # IO_L83N_VREF_3 , SV2 Pin 34</v>
+      </c>
+      <c r="J15" s="27"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="20"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B16" s="12">
-        <v>34</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>178</v>
+      <c r="B16" s="11">
+        <v>32</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>174</v>
       </c>
       <c r="E16" s="1">
-        <v>17</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>247</v>
+        <v>18</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H16" s="4">
-        <v>5</v>
-      </c>
-      <c r="I16" s="21" t="str">
+        <v>6</v>
+      </c>
+      <c r="I16" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;  # IO_L83N_VREF_3 , SV2 Pin 34</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K16" s="4">
-        <v>5</v>
-      </c>
-      <c r="L16" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;  # IO_L83N_VREF_3 , SV2 Pin 34</v>
-      </c>
-      <c r="M16" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N16" s="4">
-        <v>5</v>
-      </c>
-      <c r="O16" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;5&gt;" LOC = P1 | IOSTANDARD = LVCMOS33;  # IO_L83N_VREF_3 , SV2 Pin 34</v>
-      </c>
+        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;  # IO_L52N_3 , SV2 Pin 32</v>
+      </c>
+      <c r="J16" s="27"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="20"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B17" s="12">
-        <v>32</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>174</v>
+      <c r="B17" s="11">
+        <v>30</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="E17" s="1">
-        <v>18</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>247</v>
+        <v>19</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="H17" s="4">
-        <v>6</v>
-      </c>
-      <c r="I17" s="21" t="str">
+        <v>7</v>
+      </c>
+      <c r="I17" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;  # IO_L52N_3 , SV2 Pin 32</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K17" s="4">
-        <v>6</v>
-      </c>
-      <c r="L17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;  # IO_L52N_3 , SV2 Pin 32</v>
-      </c>
-      <c r="M17" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N17" s="4">
-        <v>6</v>
-      </c>
-      <c r="O17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;6&gt;" LOC = P5 | IOSTANDARD = LVCMOS33;  # IO_L52N_3 , SV2 Pin 32</v>
-      </c>
+        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;  # IO_L51N_3 , SV2 Pin 30</v>
+      </c>
+      <c r="J17" s="27"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="20"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B18" s="12">
-        <v>30</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>170</v>
+      <c r="B18" s="11">
+        <v>26</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>162</v>
       </c>
       <c r="E18" s="1">
-        <v>19</v>
-      </c>
-      <c r="G18" s="28" t="s">
-        <v>247</v>
+        <v>21</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>244</v>
       </c>
       <c r="H18" s="4">
-        <v>7</v>
-      </c>
-      <c r="I18" s="21" t="str">
+        <v>10</v>
+      </c>
+      <c r="I18" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;  # IO_L51N_3 , SV2 Pin 30</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="K18" s="4">
-        <v>7</v>
-      </c>
-      <c r="L18" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;  # IO_L51N_3 , SV2 Pin 30</v>
-      </c>
-      <c r="M18" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N18" s="4">
-        <v>7</v>
-      </c>
-      <c r="O18" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "D&lt;7&gt;" LOC = P7 | IOSTANDARD = LVCMOS33;  # IO_L51N_3 , SV2 Pin 30</v>
-      </c>
+        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;  # IO_L49N_3 , SV2 Pin 26</v>
+      </c>
+      <c r="J18" s="27"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="20"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B19" s="12">
-        <v>26</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>162</v>
+      <c r="B19" s="11">
+        <v>20</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>150</v>
       </c>
       <c r="E19" s="1">
-        <v>21</v>
-      </c>
-      <c r="G19" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H19" s="4">
-        <v>10</v>
-      </c>
-      <c r="I19" s="21" t="str">
+        <v>9</v>
+      </c>
+      <c r="I19" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;  # IO_L49N_3 , SV2 Pin 26</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K19" s="4">
-        <v>10</v>
-      </c>
-      <c r="L19" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;  # IO_L49N_3 , SV2 Pin 26</v>
-      </c>
-      <c r="M19" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N19" s="4">
-        <v>10</v>
-      </c>
-      <c r="O19" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;10&gt;" LOC = P11 | IOSTANDARD = LVCMOS33;  # IO_L49N_3 , SV2 Pin 26</v>
-      </c>
+        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;  # IO_L42N_GCLK24_3 , SV2 Pin 20</v>
+      </c>
+      <c r="J19" s="27"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="20"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B20" s="12">
-        <v>22</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>154</v>
+      <c r="B20" s="11">
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>146</v>
       </c>
       <c r="E20" s="1">
-        <v>23</v>
-      </c>
-      <c r="G20" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>244</v>
       </c>
       <c r="H20" s="4">
-        <v>11</v>
-      </c>
-      <c r="I20" s="21" t="str">
+        <v>8</v>
+      </c>
+      <c r="I20" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;  # IO_L43N_GCLK22_IRDY2_3 , SV2 Pin 22</v>
-      </c>
-      <c r="J20" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K20" s="4">
-        <v>11</v>
-      </c>
-      <c r="L20" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;  # IO_L43N_GCLK22_IRDY2_3 , SV2 Pin 22</v>
-      </c>
-      <c r="M20" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N20" s="4">
-        <v>11</v>
-      </c>
-      <c r="O20" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;11&gt;" LOC = P16 | IOSTANDARD = LVCMOS33;  # IO_L43N_GCLK22_IRDY2_3 , SV2 Pin 22</v>
-      </c>
+        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;  # IO_L41N_GCLK26_3 , SV2 Pin 18</v>
+      </c>
+      <c r="J20" s="27"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="20"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="12">
-        <v>20</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" s="1">
-        <v>24</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="H21" s="4">
-        <v>9</v>
-      </c>
-      <c r="I21" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;  # IO_L42N_GCLK24_3 , SV2 Pin 20</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K21" s="4">
-        <v>9</v>
-      </c>
-      <c r="L21" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;  # IO_L42N_GCLK24_3 , SV2 Pin 20</v>
-      </c>
-      <c r="M21" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N21" s="4">
-        <v>9</v>
-      </c>
-      <c r="O21" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;9&gt;" LOC = P21 | IOSTANDARD = LVCMOS33;  # IO_L42N_GCLK24_3 , SV2 Pin 20</v>
-      </c>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B22" s="12">
-        <v>18</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E22" s="1">
-        <v>25</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="H22" s="4">
-        <v>8</v>
-      </c>
-      <c r="I22" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;  # IO_L41N_GCLK26_3 , SV2 Pin 18</v>
-      </c>
-      <c r="J22" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K22" s="4">
-        <v>8</v>
-      </c>
-      <c r="L22" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;  # IO_L41N_GCLK26_3 , SV2 Pin 18</v>
-      </c>
-      <c r="M22" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N22" s="4">
-        <v>8</v>
-      </c>
-      <c r="O22" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;8&gt;" LOC = P23 | IOSTANDARD = LVCMOS33;  # IO_L41N_GCLK26_3 , SV2 Pin 18</v>
-      </c>
+      <c r="B22" s="11">
+        <v>11</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="20">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22" s="14" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,H22,""" LOC = ",$C22," | IOSTANDARD = LVCMOS33;  # ",$D22,", ",$A22," Pin ",$B22)</f>
+        <v>NET "PIN_1" LOC = P33 | IOSTANDARD = LVCMOS33;  # IO_L2P_3 , SV2 Pin 11</v>
+      </c>
+      <c r="J22" s="27"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="20"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
+        <v>13</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="I23" s="14" t="str">
+        <f t="shared" ref="I23:I24" si="1" xml:space="preserve"> CONCATENATE("NET """,H23,""" LOC = ",$C23," | IOSTANDARD = LVCMOS33;  # ",$D23,", ",$A23," Pin ",$B23)</f>
+        <v>NET "PIN_2" LOC = P30 | IOSTANDARD = LVCMOS33;  # IO_L36P_3 , SV2 Pin 13</v>
+      </c>
+      <c r="J23" s="27"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="20"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" s="11">
         <v>16</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D24" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E24" s="1">
         <v>26</v>
       </c>
-      <c r="G23" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="H23" s="4">
-        <v>13</v>
-      </c>
-      <c r="I23" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;  # IO_L37N_3 , SV2 Pin 16</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="K23" s="4">
-        <v>13</v>
-      </c>
-      <c r="L23" s="21" t="str">
+      <c r="G24" s="27"/>
+      <c r="H24" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="I24" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;  # IO_L37N_3 , SV2 Pin 16</v>
-      </c>
-      <c r="M23" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="N23" s="4">
-        <v>13</v>
-      </c>
-      <c r="O23" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v>NET "A&lt;13&gt;" LOC = P26 | IOSTANDARD = LVCMOS33;  # IO_L37N_3 , SV2 Pin 16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L24" s="21"/>
+        <v>NET "PIN_26" LOC = P26 | IOSTANDARD = LVCMOS33;  # IO_L37N_3 , SV2 Pin 16</v>
+      </c>
+      <c r="J24" s="27"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="20"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>14</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="20">
         <v>27</v>
       </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="H25" s="20">
-        <v>14</v>
-      </c>
-      <c r="I25" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,G25,"&lt;",H25,"&gt;"" LOC = ",$C25," | IOSTANDARD = LVCMOS33;  # ",$D25,", ",$A25," Pin ",$B25)</f>
-        <v>NET "A&lt;14&gt;" LOC = P29 | IOSTANDARD = LVCMOS33;  # IO_L36N_3 , SV2 Pin 14</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="K25" s="20">
-        <v>14</v>
-      </c>
-      <c r="L25" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>NET "A&lt;14&gt;" LOC = P29 | IOSTANDARD = LVCMOS33;  # IO_L36N_3 , SV2 Pin 14</v>
-      </c>
-      <c r="M25" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="N25" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="O25" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,N25,""" LOC = ",$C25," | IOSTANDARD = LVCMOS33;")</f>
-        <v>NET "WE" LOC = P29 | IOSTANDARD = LVCMOS33;</v>
-      </c>
+      <c r="F25" s="20"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="I25" s="14" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,H25,""" LOC = ",$C25," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D25,", ",$A25," Pin ",$B25)</f>
+        <v>NET "PIN_27" LOC = P29 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L36N_3 , SV2 Pin 14</v>
+      </c>
+      <c r="J25" s="27"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="20"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B26" s="12">
-        <v>11</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" s="21">
-        <v>1</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="H26" s="20">
-        <v>15</v>
-      </c>
-      <c r="I26" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,G26,"&lt;",H26,"&gt;"" LOC = ",$C26," | IOSTANDARD = LVCMOS33;  # ",$D26,", ",$A26," Pin ",$B26)</f>
-        <v>NET "A&lt;15&gt;" LOC = P33 | IOSTANDARD = LVCMOS33;  # IO_L2P_3 , SV2 Pin 11</v>
-      </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="L26" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,K26,""" LOC = ",$C26," | IOSTANDARD = LVCMOS33;  # ",$D26,", ",$A26," Pin ",$B26)</f>
-        <v>NET "VPP" LOC = P33 | IOSTANDARD = LVCMOS33;  # IO_L2P_3 , SV2 Pin 11</v>
-      </c>
-      <c r="M26" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="N26" s="20">
-        <v>14</v>
-      </c>
-      <c r="O26" s="21" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,M26,"&lt;",N26,"&gt;"" LOC = ",$C26," | IOSTANDARD = LVCMOS33;  # ",$D26,", ",$A26," Pin ",$B26)</f>
-        <v>NET "A&lt;14&gt;" LOC = P33 | IOSTANDARD = LVCMOS33;  # IO_L2P_3 , SV2 Pin 11</v>
-      </c>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="O26" s="20"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="21"/>
+      <c r="A27" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B27" s="11">
+        <v>28</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="20">
+        <v>20</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="I27" s="14" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,H27,""" LOC = ",$C27," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D27,", ",$A27," Pin ",$B27)</f>
+        <v>NET "PIN_22" LOC = P9 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L50N_3 , SV2 Pin 28</v>
+      </c>
+      <c r="J27" s="27"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="14"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B28" s="12">
-        <v>28</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="E28" s="21">
-        <v>20</v>
-      </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="I28" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,H28,""" LOC = ",$C32," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D32,", ",$A32," Pin ",$B32)</f>
-        <v>NET "CE" LOC = P123 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37N_0 PULLUP, SV2 Pin 50</v>
-      </c>
-      <c r="J28" s="30"/>
-      <c r="K28" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="L28" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,K28,""" LOC = ",$C32," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D32,", ",$A32," Pin ",$B32)</f>
-        <v>NET "CE" LOC = P123 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37N_0 PULLUP, SV2 Pin 50</v>
-      </c>
-      <c r="M28" s="30"/>
-      <c r="N28" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="O28" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,N28,""" LOC = ",$C32," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D32,", ",$A32," Pin ",$B32)</f>
-        <v>NET "CE" LOC = P123 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37N_0 PULLUP, SV2 Pin 50</v>
-      </c>
+      <c r="B28" s="11">
+        <v>24</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" s="20">
+        <v>22</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="I28" s="14" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,H28,""" LOC = ",$C28," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D28,", ",$A28," Pin ",$B28)</f>
+        <v>NET "PIN_20" LOC = P14 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L44N_GCLK20_3 , SV2 Pin 24</v>
+      </c>
+      <c r="J28" s="27"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="14"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B29" s="12">
-        <v>24</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="21">
+      <c r="B29" s="11">
         <v>22</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="I29" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,H29,""" LOC = ",$C33," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D33,", ",$A33," Pin ",$B33)</f>
-        <v>NET "OE" LOC = P124 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37P_0 PULLUP, SV2 Pin 49</v>
-      </c>
-      <c r="J29" s="30"/>
-      <c r="K29" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="L29" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,K29,""" LOC = ",$C33," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D33,", ",$A33," Pin ",$B33)</f>
-        <v>NET "OE" LOC = P124 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37P_0 PULLUP, SV2 Pin 49</v>
-      </c>
-      <c r="M29" s="30"/>
-      <c r="N29" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="O29" s="15" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,N29,""" LOC = ",$C33," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D33,", ",$A33," Pin ",$B33)</f>
-        <v>NET "OE" LOC = P124 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37P_0 PULLUP, SV2 Pin 49</v>
-      </c>
+      <c r="C29" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="1">
+        <v>23</v>
+      </c>
+      <c r="G29" s="27"/>
+      <c r="H29" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="I29" s="14" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,H29,""" LOC = ",$C29," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D29,", ",$A29," Pin ",$B29)</f>
+        <v>NET "PIN_23" LOC = P16 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L43N_GCLK22_IRDY2_3 , SV2 Pin 22</v>
+      </c>
+      <c r="J29" s="27"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="20"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="15"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="14"/>
+      <c r="L30" s="20"/>
+      <c r="O30" s="14"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="34" t="s">
-        <v>274</v>
-      </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="15"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="14"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="B32" s="34">
-        <v>50</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="I32" s="36" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,H32,""" LOC = ",$C32," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D32,", ",$A32," Pin ",$B32)</f>
-        <v>NET "VPP" LOC = P123 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37N_0 PULLUP, SV2 Pin 50</v>
-      </c>
-      <c r="N32" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="O32" s="36" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,N32,""" LOC = ",$C32," | IOSTANDARD = LVCMOS33| PULLUP;  # ",$D32,", ",$A32," Pin ",$B32)</f>
-        <v>NET "VPP" LOC = P123 | IOSTANDARD = LVCMOS33| PULLUP;  # IO_L37N_0 PULLUP, SV2 Pin 50</v>
-      </c>
+      <c r="A32" s="35"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="14"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="B33" s="34">
-        <v>49</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H33" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="I33" s="36" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,H33,""" LOC = ",$C33," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D33,", ",$A33," Pin ",$B33)</f>
-        <v>NET "WE" LOC = P124 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37P_0 PULLUP, SV2 Pin 49</v>
-      </c>
-      <c r="K33" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="L33" s="36" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,K33,""" LOC = ",$C33," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D33,", ",$A33," Pin ",$B33)</f>
-        <v>NET "WE" LOC = P124 | IOSTANDARD = LVCMOS33 | PULLUP;  # IO_L37P_0 PULLUP, SV2 Pin 49</v>
-      </c>
-      <c r="O33" s="1"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="14"/>
+      <c r="L33" s="20"/>
+      <c r="O33" s="14"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="B34" s="34">
-        <v>48</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="J34" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="K34" s="39">
-        <v>15</v>
-      </c>
-      <c r="L34" s="37" t="str">
-        <f xml:space="preserve"> CONCATENATE("NET """,J34,"&lt;",K34,"&gt;"" LOC = ",$C34," | IOSTANDARD = LVCMOS33 | PULLDOWN;  # ",$D34,", ",$A34," Pin ",$B34)</f>
-        <v>NET "A&lt;15&gt;" LOC = P126 | IOSTANDARD = LVCMOS33 | PULLDOWN;  # IO_L36N_GCLK14_0 PULLDOWN, SV2 Pin 48</v>
-      </c>
-      <c r="O34" s="1"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="14"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O35" s="1"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="14"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="35"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="14"/>
+      <c r="O36" s="14"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="35"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="14"/>
+      <c r="O37" s="14"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="35"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="14"/>
+      <c r="O38" s="14"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="35"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="14"/>
+      <c r="O39" s="14"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="35"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="14"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="35"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="14"/>
     </row>
   </sheetData>
   <sortState ref="A2:L33">
